--- a/src/jira_cards.xlsx
+++ b/src/jira_cards.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H103"/>
+  <dimension ref="A1:H109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,7 +471,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TENSYLON-816</t>
+          <t>TENSYLON-818</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -481,39 +481,34 @@
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/TENSYLON-816</t>
+          <t>https://carboncars.atlassian.net/browse/TENSYLON-818</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>30963</t>
+          <t>31070</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aguardando montagem</t>
+          <t>Liberado Engenharia</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>VOLVO - EX30 ULTRA SUV - 2026</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
+          <t>MINI - COOPER 02 PORTAS HATCH - 2025</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TENSYLON-812</t>
+          <t>TENSYLON-816</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -523,12 +518,12 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/TENSYLON-812</t>
+          <t>https://carboncars.atlassian.net/browse/TENSYLON-816</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>30948</t>
+          <t>30963</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -543,19 +538,19 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>BMW - X3 SUV - 2026</t>
+          <t>VOLVO - EX30 ULTRA SUV - 2026</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TENSYLON-801</t>
+          <t>TENSYLON-815</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -565,39 +560,34 @@
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/TENSYLON-801</t>
+          <t>https://carboncars.atlassian.net/browse/TENSYLON-815</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>30864</t>
+          <t>30956</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aguardando montagem</t>
+          <t>A Produzir</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>KIA - CARNIVAL VAN - 2025</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
+          <t>LAND ROVER - NEW DISCOVERY SUV - 2026</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TENSYLON-799</t>
+          <t>TENSYLON-813</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -607,39 +597,34 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/TENSYLON-799</t>
+          <t>https://carboncars.atlassian.net/browse/TENSYLON-813</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>30840</t>
+          <t>30949</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aguardando Autoclave</t>
+          <t>Liberado Engenharia</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>PORSCHE - CAYENNE COUPE - 2026</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
+          <t>BMW - SERIE 3 SEDAN - 2026</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TENSYLON-796</t>
+          <t>TENSYLON-812</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -649,17 +634,17 @@
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/TENSYLON-796</t>
+          <t>https://carboncars.atlassian.net/browse/TENSYLON-812</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>30828</t>
+          <t>30948</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aguardando Acabamento</t>
+          <t>Aguardando montagem</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -669,19 +654,19 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>BMW - X6 SUV - 2026</t>
+          <t>BMW - X3 SUV - 2026</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>11/03/2026</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TENSYLON-794</t>
+          <t>TENSYLON-805</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -691,39 +676,34 @@
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/TENSYLON-794</t>
+          <t>https://carboncars.atlassian.net/browse/TENSYLON-805</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>30822</t>
+          <t>30905</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aguardando Acabamento</t>
+          <t>Liberado Engenharia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>PORSCHE - CAYENNE COUPE - 2025</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
+          <t>BMW - X3 SUV - 2026</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TENSYLON-761</t>
+          <t>TENSYLON-801</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -733,12 +713,12 @@
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/TENSYLON-761</t>
+          <t>https://carboncars.atlassian.net/browse/TENSYLON-801</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>30628</t>
+          <t>30864</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -753,7 +733,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>BMW - X3 SUV - 2026</t>
+          <t>KIA - CARNIVAL VAN - 2025</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -765,7 +745,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TENSYLON-752</t>
+          <t>TENSYLON-799</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -775,17 +755,17 @@
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/TENSYLON-752</t>
+          <t>https://carboncars.atlassian.net/browse/TENSYLON-799</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>30580</t>
+          <t>30840</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aguardando Acabamento</t>
+          <t>Aguardando Autoclave</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -795,7 +775,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>AUDI - SQ6 E-TRON SPORTBACK - 2025</t>
+          <t>PORSCHE - CAYENNE COUPE - 2026</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -807,7 +787,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TENSYLON-746</t>
+          <t>TENSYLON-796</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -817,12 +797,12 @@
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/TENSYLON-746</t>
+          <t>https://carboncars.atlassian.net/browse/TENSYLON-796</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>30538</t>
+          <t>30828</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -837,7 +817,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>PORSCHE - 911 - 2025</t>
+          <t>BMW - X6 SUV - 2026</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -849,7 +829,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TENSYLON-730</t>
+          <t>TENSYLON-794</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -859,39 +839,39 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/TENSYLON-730</t>
+          <t>https://carboncars.atlassian.net/browse/TENSYLON-794</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>30483</t>
+          <t>30822</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aguardando montagem</t>
+          <t>Aguardando Acabamento</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>⚪️RECEBIDO ENCAMINHADO</t>
+          <t>🟢RECEBIDO LIBERADO</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>JEEP - COMMANDER SUV - 2026</t>
+          <t>PORSCHE - CAYENNE COUPE - 2025</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TENSYLON-691</t>
+          <t>TENSYLON-761</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -901,17 +881,17 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/TENSYLON-691</t>
+          <t>https://carboncars.atlassian.net/browse/TENSYLON-761</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>30351</t>
+          <t>30628</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aguardando Acabamento</t>
+          <t>Aguardando montagem</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -921,19 +901,19 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>GWM - HAVAL H9 SUV - 2026</t>
+          <t>BMW - X3 SUV - 2026</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>11/03/2026</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TENSYLON-674</t>
+          <t>TENSYLON-752</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -943,12 +923,12 @@
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/TENSYLON-674</t>
+          <t>https://carboncars.atlassian.net/browse/TENSYLON-752</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>30281</t>
+          <t>30580</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -963,7 +943,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>MERCEDES-BENZ - GLS SUV - 2026</t>
+          <t>AUDI - SQ6 E-TRON SPORTBACK - 2025</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -975,27 +955,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MANTA-30763</t>
+          <t>TENSYLON-746</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Manta</t>
+          <t>Tensylon</t>
         </is>
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30763</t>
+          <t>https://carboncars.atlassian.net/browse/TENSYLON-746</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>31136 - ALT</t>
+          <t>30538</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Liberado Engenharia</t>
+          <t>Aguardando Acabamento</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1005,34 +985,34 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA SEDAN - 2026</t>
+          <t>PORSCHE - 911 - 2025</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MANTA-30759</t>
+          <t>TENSYLON-745</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Manta</t>
+          <t>Tensylon</t>
         </is>
       </c>
       <c r="C15" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30759</t>
+          <t>https://carboncars.atlassian.net/browse/TENSYLON-745</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>30993 - ALT</t>
+          <t>30529</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1047,29 +1027,29 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>BMW - X1 SUV - 2026</t>
+          <t>GWM - HAVAL H6 PHEV 19 - 2026</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MANTA-30740</t>
+          <t>TENSYLON-739</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Manta</t>
+          <t>Tensylon</t>
         </is>
       </c>
       <c r="C16" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30740</t>
+          <t>https://carboncars.atlassian.net/browse/TENSYLON-739</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>31140</t>
+          <t>30510</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1079,86 +1059,81 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA SEDAN - 2026</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>13/03/2026</t>
+          <t>GWM - WEY 07 SUV - 2026</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MANTA-30739</t>
+          <t>TENSYLON-730</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Manta</t>
+          <t>Tensylon</t>
         </is>
       </c>
       <c r="C17" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30739</t>
+          <t>https://carboncars.atlassian.net/browse/TENSYLON-730</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>31139</t>
+          <t>30483</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Liberado Engenharia</t>
+          <t>Aguardando montagem</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA SEDAN - 2026</t>
+          <t>JEEP - COMMANDER SUV - 2026</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>11/03/2026</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MANTA-30738</t>
+          <t>TENSYLON-728</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Manta</t>
+          <t>Tensylon</t>
         </is>
       </c>
       <c r="C18" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30738</t>
+          <t>https://carboncars.atlassian.net/browse/TENSYLON-728</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>31138</t>
+          <t>30472</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Liberado Engenharia</t>
+          <t>A Produzir</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1168,39 +1143,39 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA SEDAN - 2026</t>
+          <t>LAND ROVER - DISCOVERY SPORT SUV - 2023</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MANTA-30737</t>
+          <t>TENSYLON-691</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Manta</t>
+          <t>Tensylon</t>
         </is>
       </c>
       <c r="C19" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30737</t>
+          <t>https://carboncars.atlassian.net/browse/TENSYLON-691</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>31137</t>
+          <t>30351</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Liberado Engenharia</t>
+          <t>Aguardando Acabamento</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1210,39 +1185,39 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA SEDAN - 2026</t>
+          <t>GWM - HAVAL H9 SUV - 2026</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MANTA-30735</t>
+          <t>TENSYLON-674</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Manta</t>
+          <t>Tensylon</t>
         </is>
       </c>
       <c r="C20" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30735</t>
+          <t>https://carboncars.atlassian.net/browse/TENSYLON-674</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>31135</t>
+          <t>30281</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Liberado Engenharia</t>
+          <t>Aguardando Acabamento</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1252,19 +1227,19 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA SEDAN - 2026</t>
+          <t>MERCEDES-BENZ - GLS SUV - 2026</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MANTA-30734</t>
+          <t>MANTA-30763</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1274,17 +1249,17 @@
       </c>
       <c r="C21" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30734</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30763</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>31134</t>
+          <t>31136 - ALT</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>A Produzir</t>
+          <t>Liberado Engenharia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1299,14 +1274,14 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MANTA-30733</t>
+          <t>MANTA-30759</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1316,12 +1291,12 @@
       </c>
       <c r="C22" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30733</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30759</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>31133</t>
+          <t>30993 - ALT</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1331,24 +1306,19 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA SEDAN - 2026</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>13/03/2026</t>
+          <t>BMW - X1 SUV - 2026</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MANTA-30732</t>
+          <t>MANTA-30740</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1358,12 +1328,12 @@
       </c>
       <c r="C23" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30732</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30740</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>31132</t>
+          <t>31140</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1378,7 +1348,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA CROSS - 2026</t>
+          <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1390,7 +1360,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MANTA-30730</t>
+          <t>MANTA-30739</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1400,12 +1370,12 @@
       </c>
       <c r="C24" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30730</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30739</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>31130</t>
+          <t>31139</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1420,7 +1390,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA CROSS - 2026</t>
+          <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1432,7 +1402,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MANTA-30722</t>
+          <t>MANTA-30738</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1442,12 +1412,12 @@
       </c>
       <c r="C25" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30722</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30738</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>31122</t>
+          <t>31138</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1457,19 +1427,24 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>⚪️RECEBIDO ENCAMINHADO</t>
+          <t>🟢RECEBIDO LIBERADO</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>TOYOTA - SW4 SUV - 2026</t>
+          <t>TOYOTA - COROLLA SEDAN - 2026</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>13/03/2026</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MANTA-30720</t>
+          <t>MANTA-30737</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1479,12 +1454,12 @@
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30720</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30737</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>30931 - ALT</t>
+          <t>31137</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1499,7 +1474,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA CROSS - 2026</t>
+          <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1511,7 +1486,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MANTA-30718</t>
+          <t>MANTA-30735</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1521,12 +1496,12 @@
       </c>
       <c r="C27" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30718</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30735</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>31120</t>
+          <t>31135</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1541,7 +1516,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA CROSS - 2026</t>
+          <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1553,7 +1528,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>MANTA-30670</t>
+          <t>MANTA-30734</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1563,34 +1538,39 @@
       </c>
       <c r="C28" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30670</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30734</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>31073</t>
+          <t>31134</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Liberado Engenharia</t>
+          <t>A Produzir</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>⚪️RECEBIDO ENCAMINHADO</t>
+          <t>🟢RECEBIDO LIBERADO</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>GWM - HAVAL H6 HEV 2 - 2026</t>
+          <t>TOYOTA - COROLLA SEDAN - 2026</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>11/03/2026</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MANTA-30667</t>
+          <t>MANTA-30733</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1600,12 +1580,12 @@
       </c>
       <c r="C29" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30667</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30733</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>31070</t>
+          <t>31133</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1615,19 +1595,24 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>⚪️RECEBIDO ENCAMINHADO</t>
+          <t>🟢RECEBIDO LIBERADO</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>MINI - COOPER 02 PORTAS HATCH - 2025</t>
+          <t>TOYOTA - COROLLA SEDAN - 2026</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>13/03/2026</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MANTA-30658</t>
+          <t>MANTA-30732</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1637,12 +1622,12 @@
       </c>
       <c r="C30" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30658</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30732</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>31061</t>
+          <t>31132</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1669,7 +1654,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MANTA-30657</t>
+          <t>MANTA-30730</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1679,12 +1664,12 @@
       </c>
       <c r="C31" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30657</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30730</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>31060</t>
+          <t>31130</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1711,7 +1696,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MANTA-30656</t>
+          <t>MANTA-30722</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1721,12 +1706,12 @@
       </c>
       <c r="C32" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30656</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30722</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>31059</t>
+          <t>31122</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1736,24 +1721,19 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA CROSS - 2026</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>13/03/2026</t>
+          <t>TOYOTA - SW4 SUV - 2026</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MANTA-30650</t>
+          <t>MANTA-30720</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1763,12 +1743,12 @@
       </c>
       <c r="C33" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30650</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30720</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>31055</t>
+          <t>30931 - ALT</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1778,19 +1758,24 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>⚪️RECEBIDO ENCAMINHADO</t>
+          <t>🟢RECEBIDO LIBERADO</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>FORD - TERRITORY - 2026</t>
+          <t>TOYOTA - COROLLA CROSS - 2026</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>13/03/2026</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MANTA-30649</t>
+          <t>MANTA-30718</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1800,12 +1785,12 @@
       </c>
       <c r="C34" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30649</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30718</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>31054</t>
+          <t>31120</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1820,7 +1805,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA SEDAN - 2026</t>
+          <t>TOYOTA - COROLLA CROSS - 2026</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1832,7 +1817,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MANTA-30636</t>
+          <t>MANTA-30670</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1842,12 +1827,12 @@
       </c>
       <c r="C35" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30636</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30670</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>31041</t>
+          <t>31073</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1862,14 +1847,14 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>FORD - MUSTANG GT - 2025</t>
+          <t>GWM - HAVAL H6 HEV 2 - 2026</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MANTA-30624</t>
+          <t>MANTA-30667</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1879,12 +1864,12 @@
       </c>
       <c r="C36" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30624</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30667</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>31030</t>
+          <t>31070</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1894,24 +1879,19 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA SEDAN - 2026</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>13/03/2026</t>
+          <t>MINI - COOPER 02 PORTAS HATCH - 2025</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MANTA-30622</t>
+          <t>MANTA-30658</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1921,12 +1901,12 @@
       </c>
       <c r="C37" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30622</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30658</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>31028</t>
+          <t>31061</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1941,7 +1921,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA SEDAN - 2026</t>
+          <t>TOYOTA - COROLLA CROSS - 2026</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1953,7 +1933,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MANTA-30619</t>
+          <t>MANTA-30657</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1963,12 +1943,12 @@
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30619</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30657</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>31025</t>
+          <t>31060</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1983,7 +1963,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA SEDAN - 2026</t>
+          <t>TOYOTA - COROLLA CROSS - 2026</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1995,7 +1975,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MANTA-30615</t>
+          <t>MANTA-30656</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2005,12 +1985,12 @@
       </c>
       <c r="C39" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30615</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30656</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>31021</t>
+          <t>31059</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2037,7 +2017,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MANTA-30613</t>
+          <t>MANTA-30650</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2047,12 +2027,12 @@
       </c>
       <c r="C40" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30613</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30650</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>31019</t>
+          <t>31055</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2062,24 +2042,19 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA CROSS - 2026</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>13/03/2026</t>
+          <t>FORD - TERRITORY - 2026</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MANTA-30610</t>
+          <t>MANTA-30649</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2089,12 +2064,12 @@
       </c>
       <c r="C41" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30610</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30649</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>31016</t>
+          <t>31054</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2109,7 +2084,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA CROSS - 2026</t>
+          <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2121,7 +2096,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>MANTA-30609</t>
+          <t>MANTA-30636</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2131,12 +2106,12 @@
       </c>
       <c r="C42" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30609</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30636</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>31015</t>
+          <t>31041</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2146,24 +2121,19 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA CROSS - 2026</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>13/03/2026</t>
+          <t>FORD - MUSTANG GT - 2025</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MANTA-30608</t>
+          <t>MANTA-30624</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2173,12 +2143,12 @@
       </c>
       <c r="C43" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30608</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30624</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>31014</t>
+          <t>31030</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2193,7 +2163,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA CROSS - 2026</t>
+          <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2205,7 +2175,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MANTA-30607</t>
+          <t>MANTA-30622</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2215,12 +2185,12 @@
       </c>
       <c r="C44" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30607</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30622</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>31013</t>
+          <t>31028</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2247,7 +2217,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MANTA-30606</t>
+          <t>MANTA-30619</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2257,12 +2227,12 @@
       </c>
       <c r="C45" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30606</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30619</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>31012</t>
+          <t>31025</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2277,7 +2247,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA CROSS - 2026</t>
+          <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2289,7 +2259,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MANTA-30602</t>
+          <t>MANTA-30615</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2299,12 +2269,12 @@
       </c>
       <c r="C46" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30602</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30615</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>31009</t>
+          <t>31021</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2331,7 +2301,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MANTA-30600</t>
+          <t>MANTA-30613</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2341,12 +2311,12 @@
       </c>
       <c r="C47" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30600</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30613</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>31006</t>
+          <t>31019</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2373,7 +2343,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MANTA-30595</t>
+          <t>MANTA-30610</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2383,12 +2353,12 @@
       </c>
       <c r="C48" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30595</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30610</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>31001</t>
+          <t>31016</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2403,7 +2373,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA SEDAN - 2026</t>
+          <t>TOYOTA - COROLLA CROSS - 2026</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2415,7 +2385,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MANTA-30594</t>
+          <t>MANTA-30609</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2425,12 +2395,12 @@
       </c>
       <c r="C49" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30594</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30609</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>31000</t>
+          <t>31015</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2445,7 +2415,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA SEDAN - 2026</t>
+          <t>TOYOTA - COROLLA CROSS - 2026</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2457,7 +2427,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MANTA-30593</t>
+          <t>MANTA-30608</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2467,12 +2437,12 @@
       </c>
       <c r="C50" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30593</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30608</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>30999</t>
+          <t>31014</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2487,7 +2457,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA SEDAN - 2026</t>
+          <t>TOYOTA - COROLLA CROSS - 2026</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2499,7 +2469,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>MANTA-30590</t>
+          <t>MANTA-30607</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2509,12 +2479,12 @@
       </c>
       <c r="C51" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30590</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30607</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>30996</t>
+          <t>31013</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2541,7 +2511,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>MANTA-30586</t>
+          <t>MANTA-30606</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2551,12 +2521,12 @@
       </c>
       <c r="C52" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30586</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30606</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>30992</t>
+          <t>31012</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2583,7 +2553,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MANTA-30585</t>
+          <t>MANTA-30602</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2593,12 +2563,12 @@
       </c>
       <c r="C53" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30585</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30602</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>30991</t>
+          <t>31009</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2625,7 +2595,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MANTA-30584</t>
+          <t>MANTA-30600</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2635,12 +2605,12 @@
       </c>
       <c r="C54" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30584</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30600</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>30990</t>
+          <t>31006</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2655,7 +2625,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA SEDAN - 2026</t>
+          <t>TOYOTA - COROLLA CROSS - 2026</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2667,7 +2637,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>MANTA-30583</t>
+          <t>MANTA-30595</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2677,12 +2647,12 @@
       </c>
       <c r="C55" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30583</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30595</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>30989</t>
+          <t>31001</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2709,7 +2679,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>MANTA-30582</t>
+          <t>MANTA-30594</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2719,12 +2689,12 @@
       </c>
       <c r="C56" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30582</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30594</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>30988</t>
+          <t>31000</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2751,7 +2721,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>MANTA-30581</t>
+          <t>MANTA-30593</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2761,12 +2731,12 @@
       </c>
       <c r="C57" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30581</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30593</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>30987</t>
+          <t>30999</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2793,7 +2763,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>MANTA-30580</t>
+          <t>MANTA-30590</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2803,12 +2773,12 @@
       </c>
       <c r="C58" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30580</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30590</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>30986</t>
+          <t>30996</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2835,7 +2805,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>MANTA-30579</t>
+          <t>MANTA-30586</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2845,12 +2815,12 @@
       </c>
       <c r="C59" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30579</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30586</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>30985</t>
+          <t>30992</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2865,7 +2835,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA SEDAN - 2026</t>
+          <t>TOYOTA - COROLLA CROSS - 2026</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -2877,7 +2847,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>MANTA-30578</t>
+          <t>MANTA-30585</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2887,12 +2857,12 @@
       </c>
       <c r="C60" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30578</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30585</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>30984</t>
+          <t>30991</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2907,7 +2877,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA SEDAN - 2026</t>
+          <t>TOYOTA - COROLLA CROSS - 2026</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -2919,7 +2889,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>MANTA-30577</t>
+          <t>MANTA-30584</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2929,12 +2899,12 @@
       </c>
       <c r="C61" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30577</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30584</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>30983</t>
+          <t>30990</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2961,7 +2931,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>MANTA-30576</t>
+          <t>MANTA-30583</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2971,12 +2941,12 @@
       </c>
       <c r="C62" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30576</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30583</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>30982</t>
+          <t>30989</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3003,7 +2973,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>MANTA-30575</t>
+          <t>MANTA-30582</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3013,12 +2983,12 @@
       </c>
       <c r="C63" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30575</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30582</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>30981</t>
+          <t>30988</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3045,7 +3015,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>MANTA-30574</t>
+          <t>MANTA-30581</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3055,12 +3025,12 @@
       </c>
       <c r="C64" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30574</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30581</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>30980</t>
+          <t>30987</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3075,7 +3045,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA CROSS - 2026</t>
+          <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3087,7 +3057,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>MANTA-30573</t>
+          <t>MANTA-30580</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3097,12 +3067,12 @@
       </c>
       <c r="C65" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30573</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30580</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>30979</t>
+          <t>30986</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3117,7 +3087,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA CROSS - 2026</t>
+          <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3129,7 +3099,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>MANTA-30571</t>
+          <t>MANTA-30579</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3139,12 +3109,12 @@
       </c>
       <c r="C66" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30571</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30579</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>30977</t>
+          <t>30985</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3171,7 +3141,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MANTA-30570</t>
+          <t>MANTA-30578</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3181,12 +3151,12 @@
       </c>
       <c r="C67" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30570</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30578</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>30976</t>
+          <t>30984</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3213,7 +3183,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>MANTA-30569</t>
+          <t>MANTA-30577</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3223,12 +3193,12 @@
       </c>
       <c r="C68" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30569</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30577</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>30975</t>
+          <t>30983</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3255,7 +3225,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>MANTA-30543</t>
+          <t>MANTA-30576</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3265,34 +3235,39 @@
       </c>
       <c r="C69" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30543</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30576</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>30949</t>
+          <t>30982</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>A Produzir</t>
+          <t>Liberado Engenharia</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>⚪️RECEBIDO ENCAMINHADO</t>
+          <t>🟢RECEBIDO LIBERADO</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>BMW - SERIE 3 SEDAN - 2026</t>
+          <t>TOYOTA - COROLLA SEDAN - 2026</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>13/03/2026</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>MANTA-30530</t>
+          <t>MANTA-30575</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3302,12 +3277,12 @@
       </c>
       <c r="C70" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30530</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30575</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>30939</t>
+          <t>30981</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -3322,7 +3297,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA CROSS - 2026</t>
+          <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3334,7 +3309,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>MANTA-30520</t>
+          <t>MANTA-30574</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3344,12 +3319,12 @@
       </c>
       <c r="C71" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30520</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30574</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>30929</t>
+          <t>30980</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -3359,19 +3334,24 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>⚪️RECEBIDO ENCAMINHADO</t>
+          <t>🟢RECEBIDO LIBERADO</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>VOLVO - EX30 PLUS SUV - 2026</t>
+          <t>TOYOTA - COROLLA CROSS - 2026</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>13/03/2026</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>MANTA-30512</t>
+          <t>MANTA-30573</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3381,12 +3361,12 @@
       </c>
       <c r="C72" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30512</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30573</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>30921</t>
+          <t>30979</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -3401,7 +3381,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA SEDAN - 2026</t>
+          <t>TOYOTA - COROLLA CROSS - 2026</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3413,7 +3393,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>MANTA-30511</t>
+          <t>MANTA-30571</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3423,12 +3403,12 @@
       </c>
       <c r="C73" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30511</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30571</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>30920</t>
+          <t>30977</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -3455,7 +3435,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>MANTA-30509</t>
+          <t>MANTA-30570</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3465,12 +3445,12 @@
       </c>
       <c r="C74" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30509</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30570</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>30918</t>
+          <t>30976</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -3485,7 +3465,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA CROSS - 2026</t>
+          <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3497,7 +3477,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>MANTA-30505</t>
+          <t>MANTA-30569</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3507,12 +3487,12 @@
       </c>
       <c r="C75" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30505</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30569</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>30914</t>
+          <t>30975</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -3527,7 +3507,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA CROSS - 2026</t>
+          <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3539,7 +3519,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>MANTA-30496</t>
+          <t>MANTA-30543</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3549,17 +3529,17 @@
       </c>
       <c r="C76" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30496</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30543</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>30905</t>
+          <t>30949</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Liberado Engenharia</t>
+          <t>A Produzir</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3569,14 +3549,14 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>BMW - X3 SUV - 2026</t>
+          <t>BMW - SERIE 3 SEDAN - 2026</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>MANTA-30494</t>
+          <t>MANTA-30530</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3586,12 +3566,12 @@
       </c>
       <c r="C77" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30494</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30530</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>30903</t>
+          <t>30939</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -3601,19 +3581,24 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>⚪️RECEBIDO ENCAMINHADO</t>
+          <t>🟢RECEBIDO LIBERADO</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>TOYOTA - RAV4 HEV SUV - 2025</t>
+          <t>TOYOTA - COROLLA CROSS - 2026</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>13/03/2026</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>MANTA-30463</t>
+          <t>MANTA-30520</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3623,12 +3608,12 @@
       </c>
       <c r="C78" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30463</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30520</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>30876</t>
+          <t>30929</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3638,24 +3623,19 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA SEDAN - 2026</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>13/03/2026</t>
+          <t>VOLVO - EX30 PLUS SUV - 2026</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>MANTA-30458</t>
+          <t>MANTA-30512</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3665,12 +3645,12 @@
       </c>
       <c r="C79" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30458</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30512</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>30871</t>
+          <t>30921</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3680,19 +3660,24 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>⚪️RECEBIDO ENCAMINHADO</t>
+          <t>🟢RECEBIDO LIBERADO</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>GWM - HAVAL H6 PHEV 35 - 2026</t>
+          <t>TOYOTA - COROLLA SEDAN - 2026</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>13/03/2026</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>MANTA-30452</t>
+          <t>MANTA-30511</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3702,12 +3687,12 @@
       </c>
       <c r="C80" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30452</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30511</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>30865</t>
+          <t>30920</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -3722,7 +3707,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA CROSS - 2026</t>
+          <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3734,7 +3719,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>MANTA-30447</t>
+          <t>MANTA-30509</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3744,12 +3729,12 @@
       </c>
       <c r="C81" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30447</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30509</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>30860</t>
+          <t>30918</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -3759,19 +3744,24 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>⚪️RECEBIDO ENCAMINHADO</t>
+          <t>🟢RECEBIDO LIBERADO</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>BMW - X2 SUV - 2026</t>
+          <t>TOYOTA - COROLLA CROSS - 2026</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>13/03/2026</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>MANTA-30435</t>
+          <t>MANTA-30505</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3781,12 +3771,12 @@
       </c>
       <c r="C82" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30435</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30505</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>30848</t>
+          <t>30914</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -3796,19 +3786,24 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>⚪️RECEBIDO ENCAMINHADO</t>
+          <t>🟢RECEBIDO LIBERADO</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>JEEP - COMMANDER SUV - 2022</t>
+          <t>TOYOTA - COROLLA CROSS - 2026</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>13/03/2026</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>MANTA-30428</t>
+          <t>MANTA-30496</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3818,12 +3813,12 @@
       </c>
       <c r="C83" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30428</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30496</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>30841</t>
+          <t>30905</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -3833,24 +3828,19 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA SEDAN - 2026</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>13/03/2026</t>
+          <t>BMW - X3 SUV - 2026</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>MANTA-30421</t>
+          <t>MANTA-30494</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3860,12 +3850,12 @@
       </c>
       <c r="C84" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30421</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30494</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>30834</t>
+          <t>30903</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -3875,24 +3865,19 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA SEDAN - 2026</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>13/03/2026</t>
+          <t>TOYOTA - RAV4 HEV SUV - 2025</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>MANTA-30420</t>
+          <t>MANTA-30463</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3902,12 +3887,12 @@
       </c>
       <c r="C85" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30420</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30463</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>30833</t>
+          <t>30876</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -3927,14 +3912,14 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>MANTA-30419</t>
+          <t>MANTA-30458</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3944,12 +3929,12 @@
       </c>
       <c r="C86" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30419</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30458</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>30832</t>
+          <t>30871</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -3964,14 +3949,14 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>LAND ROVER - NEW RANGE ROVER SPORT SUV - 2026</t>
+          <t>GWM - HAVAL H6 PHEV 35 - 2026</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>MANTA-30403</t>
+          <t>MANTA-30452</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3981,34 +3966,39 @@
       </c>
       <c r="C87" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30403</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30452</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>30816</t>
+          <t>30865</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>A Produzir</t>
+          <t>Liberado Engenharia</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>⚪️RECEBIDO ENCAMINHADO</t>
+          <t>🟢RECEBIDO LIBERADO</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>FIAT - PULSE - 2024</t>
+          <t>TOYOTA - COROLLA CROSS - 2026</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>13/03/2026</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>MANTA-30367</t>
+          <t>MANTA-30447</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4018,12 +4008,12 @@
       </c>
       <c r="C88" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30367</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30447</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>30786</t>
+          <t>30860</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -4033,24 +4023,19 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA SEDAN - 2026</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>13/03/2026</t>
+          <t>BMW - X2 SUV - 2026</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>MANTA-30346</t>
+          <t>MANTA-30435</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4060,12 +4045,12 @@
       </c>
       <c r="C89" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30346</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30435</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>30766</t>
+          <t>30848</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -4080,14 +4065,14 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>JEEP - COMMANDER SUV - 2026</t>
+          <t>JEEP - COMMANDER SUV - 2022</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>MANTA-30265</t>
+          <t>MANTA-30428</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4097,12 +4082,12 @@
       </c>
       <c r="C90" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30265</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30428</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>30693</t>
+          <t>30841</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -4112,19 +4097,24 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>⚪️RECEBIDO ENCAMINHADO</t>
+          <t>🟢RECEBIDO LIBERADO</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>FORD - NOVA RANGER PICK-UP - 2026</t>
+          <t>TOYOTA - COROLLA SEDAN - 2026</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>13/03/2026</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>MANTA-30257</t>
+          <t>MANTA-30421</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4134,12 +4124,12 @@
       </c>
       <c r="C91" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30257</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30421</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>30687</t>
+          <t>30834</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -4154,7 +4144,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>TOYOTA - SW4 SUV - 2026</t>
+          <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -4166,7 +4156,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>MANTA-30242</t>
+          <t>MANTA-30420</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4176,12 +4166,12 @@
       </c>
       <c r="C92" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30242</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30420</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>30674</t>
+          <t>30833</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -4196,7 +4186,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA CROSS - 2026</t>
+          <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4208,7 +4198,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>MANTA-30224</t>
+          <t>MANTA-30419</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4218,12 +4208,12 @@
       </c>
       <c r="C93" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30224</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30419</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>30657</t>
+          <t>30832</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -4233,24 +4223,19 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>TOYOTA - SW4 SUV - 2026</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>13/03/2026</t>
+          <t>LAND ROVER - NEW RANGE ROVER SPORT SUV - 2026</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>MANTA-30196</t>
+          <t>MANTA-30403</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4260,39 +4245,34 @@
       </c>
       <c r="C94" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30196</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30403</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>30632</t>
+          <t>30816</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Liberado Engenharia</t>
+          <t>A Produzir</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA SEDAN - 2026</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
+          <t>FIAT - PULSE - 2024</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>MANTA-30191</t>
+          <t>MANTA-30367</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4302,12 +4282,12 @@
       </c>
       <c r="C95" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30191</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30367</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>30628</t>
+          <t>30786</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -4322,19 +4302,19 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>BMW - X3 SUV - 2026</t>
+          <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>MANTA-30099</t>
+          <t>MANTA-30346</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4344,12 +4324,12 @@
       </c>
       <c r="C96" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30099</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30346</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>30556</t>
+          <t>30766</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -4364,14 +4344,14 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>GWM - HAVAL H6 PHEV 19 - 2026</t>
+          <t>JEEP - COMMANDER SUV - 2026</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>MANTA-30072</t>
+          <t>MANTA-30265</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4381,12 +4361,12 @@
       </c>
       <c r="C97" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30072</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30265</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>30529</t>
+          <t>30693</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -4401,14 +4381,14 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>GWM - HAVAL H6 PHEV 19 - 2026</t>
+          <t>FORD - NOVA RANGER PICK-UP - 2026</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>MANTA-30053</t>
+          <t>MANTA-30257</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4418,12 +4398,12 @@
       </c>
       <c r="C98" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30053</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30257</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>30510</t>
+          <t>30687</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -4433,19 +4413,24 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>⚪️RECEBIDO ENCAMINHADO</t>
+          <t>🟢RECEBIDO LIBERADO</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>GWM - WEY 07 SUV - 2026</t>
+          <t>TOYOTA - SW4 SUV - 2026</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>13/03/2026</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>MANTA-29923</t>
+          <t>MANTA-30242</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4455,12 +4440,12 @@
       </c>
       <c r="C99" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-29923</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30242</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>30392</t>
+          <t>30674</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -4475,19 +4460,19 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA SEDAN - 2026</t>
+          <t>TOYOTA - COROLLA CROSS - 2026</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>MANTA-29866</t>
+          <t>MANTA-30224</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4497,12 +4482,12 @@
       </c>
       <c r="C100" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-29866</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30224</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>30344</t>
+          <t>30657</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -4517,7 +4502,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>LAND ROVER - DISCOVERY METROPOLITAN - 2024</t>
+          <t>TOYOTA - SW4 SUV - 2026</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -4529,7 +4514,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>MANTA-29816</t>
+          <t>MANTA-30196</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4539,12 +4524,12 @@
       </c>
       <c r="C101" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-29816</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30196</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>30303</t>
+          <t>30632</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -4559,19 +4544,19 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>MERCEDES-BENZ - EQS 450+ SUV - 2024</t>
+          <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>MANTA-29792</t>
+          <t>MANTA-30099</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4581,12 +4566,12 @@
       </c>
       <c r="C102" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-29792</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30099</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>30282</t>
+          <t>30556</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -4596,57 +4581,294 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>MERCEDES-BENZ - EQS 450+ SUV - 2024</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
+          <t>GWM - HAVAL H6 PHEV 19 - 2026</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
+          <t>MANTA-30072</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C103" s="1" t="inlineStr">
+        <is>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30072</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>30529</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>⚪️RECEBIDO ENCAMINHADO</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>GWM - HAVAL H6 PHEV 19 - 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>MANTA-30053</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C104" s="1" t="inlineStr">
+        <is>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30053</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>30510</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>⚪️RECEBIDO ENCAMINHADO</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>GWM - WEY 07 SUV - 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>MANTA-29923</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C105" s="1" t="inlineStr">
+        <is>
+          <t>https://carboncars.atlassian.net/browse/MANTA-29923</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>30392</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>TOYOTA - COROLLA SEDAN - 2026</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>13/03/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>MANTA-29866</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C106" s="1" t="inlineStr">
+        <is>
+          <t>https://carboncars.atlassian.net/browse/MANTA-29866</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>30344</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>LAND ROVER - DISCOVERY METROPOLITAN - 2024</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>13/03/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>MANTA-29816</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C107" s="1" t="inlineStr">
+        <is>
+          <t>https://carboncars.atlassian.net/browse/MANTA-29816</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>30303</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>MERCEDES-BENZ - EQS 450+ SUV - 2024</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>11/03/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>MANTA-29792</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C108" s="1" t="inlineStr">
+        <is>
+          <t>https://carboncars.atlassian.net/browse/MANTA-29792</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>30282</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>MERCEDES-BENZ - EQS 450+ SUV - 2024</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>11/03/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
           <t>MANTA-29372</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="C103" s="1" t="inlineStr">
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C109" s="1" t="inlineStr">
         <is>
           <t>https://carboncars.atlassian.net/browse/MANTA-29372</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
+      <c r="D109" t="inlineStr">
         <is>
           <t>29901</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>🟢RECEBIDO LIBERADO</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
         <is>
           <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
+      <c r="H109" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -4756,6 +4978,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C101" r:id="rId100"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C102" r:id="rId101"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C109" r:id="rId108"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/jira_cards.xlsx
+++ b/src/jira_cards.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H109"/>
+  <dimension ref="A1:H108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4114,7 +4114,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>MANTA-30421</t>
+          <t>MANTA-30420</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="C91" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30421</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30420</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>30834</t>
+          <t>30833</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -4149,14 +4149,14 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>MANTA-30420</t>
+          <t>MANTA-30419</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="C92" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30420</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30419</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>30833</t>
+          <t>30832</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -4181,24 +4181,19 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA SEDAN - 2026</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
+          <t>LAND ROVER - NEW RANGE ROVER SPORT SUV - 2026</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>MANTA-30419</t>
+          <t>MANTA-30403</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4208,17 +4203,17 @@
       </c>
       <c r="C93" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30419</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30403</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>30832</t>
+          <t>30816</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Liberado Engenharia</t>
+          <t>A Produzir</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -4228,14 +4223,14 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>LAND ROVER - NEW RANGE ROVER SPORT SUV - 2026</t>
+          <t>FIAT - PULSE - 2024</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>MANTA-30403</t>
+          <t>MANTA-30367</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4245,34 +4240,39 @@
       </c>
       <c r="C94" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30403</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30367</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>30816</t>
+          <t>30786</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>A Produzir</t>
+          <t>Liberado Engenharia</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>⚪️RECEBIDO ENCAMINHADO</t>
+          <t>🟢RECEBIDO LIBERADO</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>FIAT - PULSE - 2024</t>
+          <t>TOYOTA - COROLLA SEDAN - 2026</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>13/03/2026</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>MANTA-30367</t>
+          <t>MANTA-30346</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4282,12 +4282,12 @@
       </c>
       <c r="C95" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30367</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30346</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>30786</t>
+          <t>30766</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -4297,24 +4297,19 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA SEDAN - 2026</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>13/03/2026</t>
+          <t>JEEP - COMMANDER SUV - 2026</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>MANTA-30346</t>
+          <t>MANTA-30265</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4324,12 +4319,12 @@
       </c>
       <c r="C96" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30346</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30265</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>30766</t>
+          <t>30693</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -4344,14 +4339,14 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>JEEP - COMMANDER SUV - 2026</t>
+          <t>FORD - NOVA RANGER PICK-UP - 2026</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>MANTA-30265</t>
+          <t>MANTA-30257</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4361,12 +4356,12 @@
       </c>
       <c r="C97" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30265</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30257</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>30693</t>
+          <t>30687</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -4376,19 +4371,24 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>⚪️RECEBIDO ENCAMINHADO</t>
+          <t>🟢RECEBIDO LIBERADO</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>FORD - NOVA RANGER PICK-UP - 2026</t>
+          <t>TOYOTA - SW4 SUV - 2026</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>13/03/2026</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>MANTA-30257</t>
+          <t>MANTA-30242</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="C98" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30257</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30242</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>30687</t>
+          <t>30674</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -4418,19 +4418,19 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>TOYOTA - SW4 SUV - 2026</t>
+          <t>TOYOTA - COROLLA CROSS - 2026</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>MANTA-30242</t>
+          <t>MANTA-30224</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="C99" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30242</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30224</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>30674</t>
+          <t>30657</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -4460,19 +4460,19 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA CROSS - 2026</t>
+          <t>TOYOTA - SW4 SUV - 2026</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>MANTA-30224</t>
+          <t>MANTA-30196</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="C100" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30224</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30196</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>30657</t>
+          <t>30632</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -4502,19 +4502,19 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>TOYOTA - SW4 SUV - 2026</t>
+          <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>MANTA-30196</t>
+          <t>MANTA-30099</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4524,12 +4524,12 @@
       </c>
       <c r="C101" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30196</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30099</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>30632</t>
+          <t>30556</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -4539,24 +4539,19 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA SEDAN - 2026</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
+          <t>GWM - HAVAL H6 PHEV 19 - 2026</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>MANTA-30099</t>
+          <t>MANTA-30072</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4566,12 +4561,12 @@
       </c>
       <c r="C102" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30099</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30072</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>30556</t>
+          <t>30529</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -4593,7 +4588,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>MANTA-30072</t>
+          <t>MANTA-30053</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4603,12 +4598,12 @@
       </c>
       <c r="C103" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30072</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30053</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>30529</t>
+          <t>30510</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -4623,14 +4618,14 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>GWM - HAVAL H6 PHEV 19 - 2026</t>
+          <t>GWM - WEY 07 SUV - 2026</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>MANTA-30053</t>
+          <t>MANTA-29923</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4640,12 +4635,12 @@
       </c>
       <c r="C104" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30053</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-29923</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>30510</t>
+          <t>30392</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -4655,19 +4650,24 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>⚪️RECEBIDO ENCAMINHADO</t>
+          <t>🟢RECEBIDO LIBERADO</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>GWM - WEY 07 SUV - 2026</t>
+          <t>TOYOTA - COROLLA SEDAN - 2026</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>13/03/2026</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>MANTA-29923</t>
+          <t>MANTA-29866</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="C105" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-29923</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-29866</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>30392</t>
+          <t>30344</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA SEDAN - 2026</t>
+          <t>LAND ROVER - DISCOVERY METROPOLITAN - 2024</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -4709,7 +4709,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>MANTA-29866</t>
+          <t>MANTA-29816</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4719,12 +4719,12 @@
       </c>
       <c r="C106" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-29866</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-29816</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>30344</t>
+          <t>30303</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -4739,19 +4739,19 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>LAND ROVER - DISCOVERY METROPOLITAN - 2024</t>
+          <t>MERCEDES-BENZ - EQS 450+ SUV - 2024</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>11/03/2026</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>MANTA-29816</t>
+          <t>MANTA-29792</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="C107" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-29816</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-29792</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>30303</t>
+          <t>30282</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -4793,7 +4793,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>MANTA-29792</t>
+          <t>MANTA-29372</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4803,12 +4803,12 @@
       </c>
       <c r="C108" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-29792</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-29372</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>30282</t>
+          <t>29901</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -4823,52 +4823,10 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>MERCEDES-BENZ - EQS 450+ SUV - 2024</t>
+          <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>MANTA-29372</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="C109" s="1" t="inlineStr">
-        <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-29372</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>29901</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>🟢RECEBIDO LIBERADO</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>TOYOTA - COROLLA SEDAN - 2026</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
         <is>
           <t>13/03/2026</t>
         </is>
@@ -4983,7 +4941,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C106" r:id="rId105"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C107" r:id="rId106"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C108" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C109" r:id="rId108"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
